--- a/example/excel/monster.xlsx
+++ b/example/excel/monster.xlsx
@@ -868,7 +868,7 @@
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>item:1004;rate:0.05;count:1|item:1003;rate:0.5;count:1</t>
+          <t>item:1004;rate:0.05;count:1;weight:3|item:1003;rate:0.5;count:1</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
